--- a/Indomie Clients Details/4 Season.xlsx
+++ b/Indomie Clients Details/4 Season.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6CC649F-A219-4162-AA6C-7149E0EF0510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49B18072-0B08-414B-9208-97EEBBE2F6FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="13" r:id="rId1"/>
@@ -3380,7 +3380,7 @@
       <c r="M4" s="231"/>
       <c r="N4" s="245">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="245"/>
       <c r="P4" s="245"/>
@@ -3408,7 +3408,7 @@
       <c r="M5" s="231"/>
       <c r="N5" s="245">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="232"/>
       <c r="P5" s="232"/>
@@ -4625,7 +4625,7 @@
       <c r="M4" s="231"/>
       <c r="N4" s="245">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="245"/>
       <c r="P4" s="245"/>
@@ -4653,7 +4653,7 @@
       <c r="M5" s="231"/>
       <c r="N5" s="245">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="232"/>
       <c r="P5" s="232"/>
@@ -5870,7 +5870,7 @@
       <c r="M4" s="231"/>
       <c r="N4" s="245">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="245"/>
       <c r="P4" s="245"/>
@@ -5898,7 +5898,7 @@
       <c r="M5" s="231"/>
       <c r="N5" s="245">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="232"/>
       <c r="P5" s="232"/>
@@ -7115,7 +7115,7 @@
       <c r="M4" s="231"/>
       <c r="N4" s="245">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="245"/>
       <c r="P4" s="245"/>
@@ -7143,7 +7143,7 @@
       <c r="M5" s="231"/>
       <c r="N5" s="245">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="232"/>
       <c r="P5" s="232"/>
@@ -8360,7 +8360,7 @@
       <c r="M4" s="231"/>
       <c r="N4" s="245">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="245"/>
       <c r="P4" s="245"/>
@@ -8388,7 +8388,7 @@
       <c r="M5" s="231"/>
       <c r="N5" s="245">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="232"/>
       <c r="P5" s="232"/>
@@ -9605,7 +9605,7 @@
       <c r="M4" s="231"/>
       <c r="N4" s="245">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="245"/>
       <c r="P4" s="245"/>
@@ -9633,7 +9633,7 @@
       <c r="M5" s="231"/>
       <c r="N5" s="245">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="232"/>
       <c r="P5" s="232"/>
@@ -10850,7 +10850,7 @@
       <c r="M4" s="231"/>
       <c r="N4" s="245">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="245"/>
       <c r="P4" s="245"/>
@@ -10878,7 +10878,7 @@
       <c r="M5" s="231"/>
       <c r="N5" s="245">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="232"/>
       <c r="P5" s="232"/>
@@ -12095,7 +12095,7 @@
       <c r="M4" s="231"/>
       <c r="N4" s="245">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="245"/>
       <c r="P4" s="245"/>
@@ -12123,7 +12123,7 @@
       <c r="M5" s="231"/>
       <c r="N5" s="245">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="232"/>
       <c r="P5" s="232"/>
@@ -13340,7 +13340,7 @@
       <c r="M4" s="231"/>
       <c r="N4" s="245">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="245"/>
       <c r="P4" s="245"/>
@@ -13368,7 +13368,7 @@
       <c r="M5" s="231"/>
       <c r="N5" s="245">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="232"/>
       <c r="P5" s="232"/>
@@ -14585,7 +14585,7 @@
       <c r="M4" s="231"/>
       <c r="N4" s="245">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="245"/>
       <c r="P4" s="245"/>
@@ -14613,7 +14613,7 @@
       <c r="M5" s="231"/>
       <c r="N5" s="245">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="232"/>
       <c r="P5" s="232"/>
@@ -18580,7 +18580,7 @@
       <c r="M4" s="231"/>
       <c r="N4" s="245">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="245"/>
       <c r="P4" s="245"/>
@@ -18608,7 +18608,7 @@
       <c r="M5" s="231"/>
       <c r="N5" s="245">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="232"/>
       <c r="P5" s="232"/>
@@ -19822,7 +19822,7 @@
       <c r="M4" s="231"/>
       <c r="N4" s="245">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="245"/>
       <c r="P4" s="245"/>
@@ -19850,7 +19850,7 @@
       <c r="M5" s="231"/>
       <c r="N5" s="245">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="232"/>
       <c r="P5" s="232"/>
@@ -21063,7 +21063,7 @@
       <c r="M4" s="231"/>
       <c r="N4" s="245">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="245"/>
       <c r="P4" s="245"/>
@@ -21091,7 +21091,7 @@
       <c r="M5" s="231"/>
       <c r="N5" s="245">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="232"/>
       <c r="P5" s="232"/>
@@ -22304,7 +22304,7 @@
       <c r="M4" s="231"/>
       <c r="N4" s="245">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="245"/>
       <c r="P4" s="245"/>
@@ -22332,7 +22332,7 @@
       <c r="M5" s="231"/>
       <c r="N5" s="245">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="232"/>
       <c r="P5" s="232"/>
@@ -23550,7 +23550,7 @@
       <c r="M4" s="231"/>
       <c r="N4" s="245">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="245"/>
       <c r="P4" s="245"/>
@@ -23578,7 +23578,7 @@
       <c r="M5" s="231"/>
       <c r="N5" s="245">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="232"/>
       <c r="P5" s="232"/>
@@ -25095,7 +25095,7 @@
       <c r="M4" s="231"/>
       <c r="N4" s="245">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="245"/>
       <c r="P4" s="245"/>
@@ -25123,7 +25123,7 @@
       <c r="M5" s="231"/>
       <c r="N5" s="245">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="232"/>
       <c r="P5" s="232"/>
@@ -26346,7 +26346,7 @@
       <c r="M4" s="231"/>
       <c r="N4" s="245">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="245"/>
       <c r="P4" s="245"/>
@@ -26374,7 +26374,7 @@
       <c r="M5" s="231"/>
       <c r="N5" s="245">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="232"/>
       <c r="P5" s="232"/>
@@ -27591,7 +27591,7 @@
       <c r="M4" s="231"/>
       <c r="N4" s="245">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="245"/>
       <c r="P4" s="245"/>
@@ -27619,7 +27619,7 @@
       <c r="M5" s="231"/>
       <c r="N5" s="245">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="232"/>
       <c r="P5" s="232"/>
@@ -28835,7 +28835,7 @@
       <c r="M4" s="231"/>
       <c r="N4" s="245">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="245"/>
       <c r="P4" s="245"/>
@@ -28863,7 +28863,7 @@
       <c r="M5" s="231"/>
       <c r="N5" s="245">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="232"/>
       <c r="P5" s="232"/>
@@ -30080,7 +30080,7 @@
       <c r="M4" s="231"/>
       <c r="N4" s="245">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="245"/>
       <c r="P4" s="245"/>
@@ -30108,7 +30108,7 @@
       <c r="M5" s="231"/>
       <c r="N5" s="245">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="232"/>
       <c r="P5" s="232"/>
@@ -31326,7 +31326,7 @@
       <c r="M4" s="231"/>
       <c r="N4" s="245">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="245"/>
       <c r="P4" s="245"/>
@@ -31354,7 +31354,7 @@
       <c r="M5" s="231"/>
       <c r="N5" s="245">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="232"/>
       <c r="P5" s="232"/>
